--- a/data/raw/profiles.xlsx
+++ b/data/raw/profiles.xlsx
@@ -659,7 +659,7 @@
     <t xml:space="preserve">grim-hammer-captain</t>
   </si>
   <si>
-    <t xml:space="preserve">ancient-enemies-orc</t>
+    <t xml:space="preserve">ancient-enemies:orc</t>
   </si>
   <si>
     <t xml:space="preserve">heavy-dwarf-armour; mattock; throwing-weapon</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">warrior; infantry; monster; beast; swarm</t>
   </si>
   <si>
-    <t xml:space="preserve">poisoned-attacks; swift-movement</t>
+    <t xml:space="preserve">poisoned-attacks:; swift-movement</t>
   </si>
   <si>
     <t xml:space="preserve">fangs-hand-weapons</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">mahud-raider</t>
   </si>
   <si>
-    <t xml:space="preserve">poisoned-attacks-blowpipe</t>
+    <t xml:space="preserve">poisoned-attacks:blowpipe</t>
   </si>
   <si>
     <t xml:space="preserve">armour; hand-weapon; shield; war-camel</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">watcher-of-karna</t>
   </si>
   <si>
-    <t xml:space="preserve">hatred:spirit; poisoned-attacks-bow; resistant-to-magic</t>
+    <t xml:space="preserve">hatred:spirit; poisoned-attacks:bow; resistant-to-magic</t>
   </si>
   <si>
     <t xml:space="preserve">light-armour; hand-weapon</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">haradrim-chieftain</t>
   </si>
   <si>
-    <t xml:space="preserve">poisoned-attacks-bow</t>
+    <t xml:space="preserve">poisoned-attacks:bow</t>
   </si>
   <si>
     <t xml:space="preserve">armour; spear; hand-weapon</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">heroic-resolve; heroic-march; heroic-strike; heroic-challenge</t>
   </si>
   <si>
-    <t xml:space="preserve">leader:serpent-guard; poisoned-attacks; leader:serpent-rider</t>
+    <t xml:space="preserve">leader:serpent-guard; poisoned-attacks:; leader:serpent-rider</t>
   </si>
   <si>
     <t xml:space="preserve">armour; hand-weapon; serpent-banner</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">gundabad</t>
   </si>
   <si>
-    <t xml:space="preserve">ancient-enemies-dwarf; ancient-enemies-elf</t>
+    <t xml:space="preserve">ancient-enemies:dwarf; ancient-enemies:elf</t>
   </si>
   <si>
     <t xml:space="preserve">azog-the-defiler</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">bolg-spawn-of-azog</t>
   </si>
   <si>
-    <t xml:space="preserve">burly; ancient-enemies-dwarf; ancient-enemies-elf</t>
+    <t xml:space="preserve">burly; ancient-enemies:dwarf; ancient-enemies:elf</t>
   </si>
   <si>
     <t xml:space="preserve">fell-warg</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">160mm</t>
   </si>
   <si>
-    <t xml:space="preserve">dominant:5; large-target; terror; ancient-enemies-dwarf; ancient-enemies-elf</t>
+    <t xml:space="preserve">dominant:5; large-target; terror; ancient-enemies:dwarf; ancient-enemies:elf</t>
   </si>
   <si>
     <t xml:space="preserve">catapult; metal-gauntlets</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">gundabad-ogre</t>
   </si>
   <si>
-    <t xml:space="preserve">ancient-enemies-dwarf; ancient-enemies-elf; dominant:3; terror</t>
+    <t xml:space="preserve">ancient-enemies:dwarf; ancient-enemies:elf; dominant:3; terror</t>
   </si>
   <si>
     <t xml:space="preserve">gundabad-orc-captain</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">80mm</t>
   </si>
   <si>
-    <t xml:space="preserve">terror; large-target; dominant:4; ancient-enemies-dwarf; ancient-enemies-elf</t>
+    <t xml:space="preserve">terror; large-target; dominant:4; ancient-enemies:dwarf; ancient-enemies:elf</t>
   </si>
   <si>
     <t xml:space="preserve">heavy-armour; crushing-club</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">mirkwood-giant-spider</t>
   </si>
   <si>
-    <t xml:space="preserve">poisoned-attacks-fangs; swift-movement; terror</t>
+    <t xml:space="preserve">poisoned-attacks:fangs; swift-movement; terror</t>
   </si>
   <si>
     <t xml:space="preserve">mirkwood-hunting-spider</t>
   </si>
   <si>
-    <t xml:space="preserve">poisoned-attacks-fangs; stalk-unseen; swift-movement; terror</t>
+    <t xml:space="preserve">poisoned-attacks:fangs; stalk-unseen; swift-movement; terror</t>
   </si>
   <si>
     <t xml:space="preserve">narzug-hunter-orc-captain</t>
   </si>
   <si>
-    <t xml:space="preserve">expert-shot; poisoned-attacks-orc-bow</t>
+    <t xml:space="preserve">expert-shot; poisoned-attacks:orc-bow</t>
   </si>
   <si>
     <t xml:space="preserve">light-armour; hand-weapon; orc-bow</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">231x133mm</t>
   </si>
   <si>
-    <t xml:space="preserve">ancient-enemies-dwarf; dominant:20; fearless; fly; harbinger-of-evil:18; large-target; monstrous-charge; resistant-to-magic; terror</t>
+    <t xml:space="preserve">ancient-enemies:dwarf; dominant:20; fearless; fly; harbinger-of-evil:18; large-target; monstrous-charge; resistant-to-magic; terror</t>
   </si>
   <si>
     <t xml:space="preserve">razor-sharp-teeth-massive-talons-hand-weapons</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">druadan</t>
   </si>
   <si>
-    <t xml:space="preserve">hatred:goblin; hated-orc; hatred:uruk-hai; poisoned-attacks; stalk-unseen; woodland-creature</t>
+    <t xml:space="preserve">hatred:goblin; hatred:orc; hatred:uruk-hai; poisoned-attacks:blowpipe; stalk-unseen; woodland-creature</t>
   </si>
   <si>
     <t xml:space="preserve">hand-weapon; spear; blowpipe</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">woses-warrior</t>
   </si>
   <si>
-    <t xml:space="preserve">hatred:goblin; hated-orc; hatred:uruk-hai; stalk-unseen; poisoned-attacks; woodland-creature</t>
+    <t xml:space="preserve">hatred:goblin; hated-orc; hatred:uruk-hai; stalk-unseen; poisoned-attacks:blowpipe; woodland-creature</t>
   </si>
   <si>
     <t xml:space="preserve">shank</t>
